--- a/ksoft_old/docs/records/Customer_Group_Records.xlsx
+++ b/ksoft_old/docs/records/Customer_Group_Records.xlsx
@@ -1345,13 +1345,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC261AE1-461F-4CC8-B41F-944546A4F782}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3228CDF1-8D10-4924-8099-4EDF67FB1F0E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FED3ACE-8C5A-433D-804E-7796B980B5F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9022D41E-414C-4778-9C56-7EBB81F89B92}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46BA665E-1BF5-451C-BB7E-C929C41773C2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1437BF46-0D70-45E6-9043-3D8ECA10D970}"/>
 </file>
--- a/ksoft_old/docs/records/Customer_Group_Records.xlsx
+++ b/ksoft_old/docs/records/Customer_Group_Records.xlsx
@@ -1345,13 +1345,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3228CDF1-8D10-4924-8099-4EDF67FB1F0E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{422076F6-5F0B-44EF-828D-043AA67B289E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9022D41E-414C-4778-9C56-7EBB81F89B92}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F14CA6F-59BC-4DE6-A4DF-B378A9236F88}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1437BF46-0D70-45E6-9043-3D8ECA10D970}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5C12D2E-BC17-40E1-830A-C659EFD6D46F}"/>
 </file>
--- a/ksoft_old/docs/records/Customer_Group_Records.xlsx
+++ b/ksoft_old/docs/records/Customer_Group_Records.xlsx
@@ -1345,13 +1345,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{422076F6-5F0B-44EF-828D-043AA67B289E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC261AE1-461F-4CC8-B41F-944546A4F782}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F14CA6F-59BC-4DE6-A4DF-B378A9236F88}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FED3ACE-8C5A-433D-804E-7796B980B5F1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5C12D2E-BC17-40E1-830A-C659EFD6D46F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46BA665E-1BF5-451C-BB7E-C929C41773C2}"/>
 </file>